--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/49.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/49.xlsx
@@ -426,13 +426,13 @@
         <v>-20.51184419329056</v>
       </c>
       <c r="E2">
-        <v>-32.95995898889238</v>
+        <v>-32.85349909344606</v>
       </c>
       <c r="F2">
-        <v>-4.823436912718734</v>
+        <v>-4.523234909209387</v>
       </c>
       <c r="G2">
-        <v>-22.47845473249766</v>
+        <v>-22.63933896934239</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.20211692466098</v>
       </c>
       <c r="E3">
-        <v>-33.35830846921411</v>
+        <v>-32.68047289432398</v>
       </c>
       <c r="F3">
-        <v>-5.347801762364848</v>
+        <v>-4.012210088217955</v>
       </c>
       <c r="G3">
-        <v>-21.76954775290028</v>
+        <v>-22.3814292638327</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.82348904098097</v>
       </c>
       <c r="E4">
-        <v>-33.94984265070305</v>
+        <v>-33.99728294440741</v>
       </c>
       <c r="F4">
-        <v>-5.442363214864023</v>
+        <v>-4.103550019887643</v>
       </c>
       <c r="G4">
-        <v>-21.67414941736788</v>
+        <v>-22.46130114078592</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.38872319734392</v>
       </c>
       <c r="E5">
-        <v>-33.84981545258463</v>
+        <v>-34.1368482490868</v>
       </c>
       <c r="F5">
-        <v>-4.939960041800929</v>
+        <v>-4.012924969286571</v>
       </c>
       <c r="G5">
-        <v>-20.48443535637445</v>
+        <v>-21.72627892270201</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.92382330025378</v>
       </c>
       <c r="E6">
-        <v>-33.90731801553402</v>
+        <v>-33.97661046056239</v>
       </c>
       <c r="F6">
-        <v>-5.267049194470341</v>
+        <v>-4.179805381152351</v>
       </c>
       <c r="G6">
-        <v>-21.31382136450975</v>
+        <v>-21.49315858219038</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.45231636088369</v>
       </c>
       <c r="E7">
-        <v>-34.51502564194136</v>
+        <v>-34.32059334618503</v>
       </c>
       <c r="F7">
-        <v>-4.62671705026931</v>
+        <v>-4.185811044822648</v>
       </c>
       <c r="G7">
-        <v>-20.86396622863311</v>
+        <v>-21.60107574567954</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.98366437596654</v>
       </c>
       <c r="E8">
-        <v>-34.36835742578094</v>
+        <v>-35.27980791777875</v>
       </c>
       <c r="F8">
-        <v>-4.683482583280951</v>
+        <v>-3.968125203408368</v>
       </c>
       <c r="G8">
-        <v>-19.70918338889731</v>
+        <v>-20.95564185570661</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.52575363251705</v>
       </c>
       <c r="E9">
-        <v>-36.21626237900993</v>
+        <v>-35.81760496245568</v>
       </c>
       <c r="F9">
-        <v>-5.125080275508951</v>
+        <v>-4.313625649972403</v>
       </c>
       <c r="G9">
-        <v>-19.90798992489439</v>
+        <v>-20.63615765843925</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.12175396090008</v>
       </c>
       <c r="E10">
-        <v>-35.19354954488065</v>
+        <v>-36.43344119970678</v>
       </c>
       <c r="F10">
-        <v>-4.590865309076147</v>
+        <v>-3.854449173089595</v>
       </c>
       <c r="G10">
-        <v>-19.01442237038924</v>
+        <v>-20.58130522939906</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.79893049738495</v>
       </c>
       <c r="E11">
-        <v>-36.02789823842388</v>
+        <v>-36.8549855238958</v>
       </c>
       <c r="F11">
-        <v>-4.751508114398847</v>
+        <v>-3.823073929341161</v>
       </c>
       <c r="G11">
-        <v>-19.45481927766018</v>
+        <v>-19.64040018422787</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.57023971818966</v>
       </c>
       <c r="E12">
-        <v>-37.57163691374267</v>
+        <v>-36.47928973479745</v>
       </c>
       <c r="F12">
-        <v>-5.066123710716904</v>
+        <v>-4.000249291288933</v>
       </c>
       <c r="G12">
-        <v>-18.84433150639979</v>
+        <v>-19.39858304058458</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.44152170678759</v>
       </c>
       <c r="E13">
-        <v>-35.80889444270193</v>
+        <v>-37.35816012054708</v>
       </c>
       <c r="F13">
-        <v>-4.627276198266199</v>
+        <v>-3.67224562100683</v>
       </c>
       <c r="G13">
-        <v>-18.3627530678931</v>
+        <v>-19.69374134922938</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-16.44619863349777</v>
       </c>
       <c r="E14">
-        <v>-38.4647923707495</v>
+        <v>-38.45096693960409</v>
       </c>
       <c r="F14">
-        <v>-4.168086467504946</v>
+        <v>-3.821994566615313</v>
       </c>
       <c r="G14">
-        <v>-18.2298048695815</v>
+        <v>-18.93743397860072</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-16.58663828213131</v>
       </c>
       <c r="E15">
-        <v>-36.09382829150155</v>
+        <v>-38.59725476394787</v>
       </c>
       <c r="F15">
-        <v>-4.213994588968095</v>
+        <v>-3.479698245165307</v>
       </c>
       <c r="G15">
-        <v>-18.5904341820837</v>
+        <v>-18.78764172458532</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.84151036121685</v>
       </c>
       <c r="E16">
-        <v>-40.00834085015997</v>
+        <v>-39.15278078436482</v>
       </c>
       <c r="F16">
-        <v>-4.353213328152191</v>
+        <v>-3.356841418921307</v>
       </c>
       <c r="G16">
-        <v>-18.66810785679885</v>
+        <v>-18.36752356401518</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-17.18564223886138</v>
       </c>
       <c r="E17">
-        <v>-39.66325754535347</v>
+        <v>-39.39974564284713</v>
       </c>
       <c r="F17">
-        <v>-3.852688063991243</v>
+        <v>-3.182909943722897</v>
       </c>
       <c r="G17">
-        <v>-18.37712580135184</v>
+        <v>-17.9311142088463</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-17.60600068527674</v>
       </c>
       <c r="E18">
-        <v>-38.56843329112605</v>
+        <v>-39.72250583503283</v>
       </c>
       <c r="F18">
-        <v>-3.933936823960027</v>
+        <v>-3.005819903617613</v>
       </c>
       <c r="G18">
-        <v>-17.74885212418172</v>
+        <v>-18.22612354294183</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-18.06333331272896</v>
       </c>
       <c r="E19">
-        <v>-40.07773292161651</v>
+        <v>-39.80003104580714</v>
       </c>
       <c r="F19">
-        <v>-3.226172259701504</v>
+        <v>-3.057846346717839</v>
       </c>
       <c r="G19">
-        <v>-18.43382882534848</v>
+        <v>-18.07257713028489</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-18.49968035678722</v>
       </c>
       <c r="E20">
-        <v>-40.04137606804593</v>
+        <v>-40.5574726652781</v>
       </c>
       <c r="F20">
-        <v>-3.470042794718276</v>
+        <v>-3.098785920498996</v>
       </c>
       <c r="G20">
-        <v>-17.64089026832778</v>
+        <v>-17.93928960105553</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-18.8746962168478</v>
       </c>
       <c r="E21">
-        <v>-40.90853808424873</v>
+        <v>-40.7951654732297</v>
       </c>
       <c r="F21">
-        <v>-3.397725492086476</v>
+        <v>-2.899344871131376</v>
       </c>
       <c r="G21">
-        <v>-17.71978387907415</v>
+        <v>-17.80214197572737</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-19.16576406366667</v>
       </c>
       <c r="E22">
-        <v>-43.5856813481033</v>
+        <v>-42.01961956016369</v>
       </c>
       <c r="F22">
-        <v>-3.309539155119246</v>
+        <v>-2.85176261914717</v>
       </c>
       <c r="G22">
-        <v>-17.74735079177966</v>
+        <v>-17.62092602345321</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-19.34596821895762</v>
       </c>
       <c r="E23">
-        <v>-41.35964655099683</v>
+        <v>-41.79408344068568</v>
       </c>
       <c r="F23">
-        <v>-2.935194127222331</v>
+        <v>-2.865762856621884</v>
       </c>
       <c r="G23">
-        <v>-17.27431190549151</v>
+        <v>-17.6723983854978</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-19.38434851515946</v>
       </c>
       <c r="E24">
-        <v>-41.5702817267526</v>
+        <v>-40.99493910407808</v>
       </c>
       <c r="F24">
-        <v>-3.183414419471202</v>
+        <v>-2.665484327810034</v>
       </c>
       <c r="G24">
-        <v>-17.65046271075459</v>
+        <v>-17.6515899515107</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-19.28474344445836</v>
       </c>
       <c r="E25">
-        <v>-41.47425543541995</v>
+        <v>-41.98895046994674</v>
       </c>
       <c r="F25">
-        <v>-3.483302471734888</v>
+        <v>-2.757064486026533</v>
       </c>
       <c r="G25">
-        <v>-17.95814646844722</v>
+        <v>-17.69109965724914</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-19.06553675991973</v>
       </c>
       <c r="E26">
-        <v>-41.42724308250932</v>
+        <v>-42.27969887937221</v>
       </c>
       <c r="F26">
-        <v>-3.180258339666536</v>
+        <v>-2.919907435171068</v>
       </c>
       <c r="G26">
-        <v>-16.67210877444316</v>
+        <v>-17.554965058856</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-18.74397913209318</v>
       </c>
       <c r="E27">
-        <v>-42.21532888559018</v>
+        <v>-42.08108000939579</v>
       </c>
       <c r="F27">
-        <v>-2.645529785443996</v>
+        <v>-2.762672533343486</v>
       </c>
       <c r="G27">
-        <v>-17.69309426093655</v>
+        <v>-17.72251011332574</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-18.32820412492813</v>
       </c>
       <c r="E28">
-        <v>-42.56168695582985</v>
+        <v>-42.2024068850093</v>
       </c>
       <c r="F28">
-        <v>-3.137449969024663</v>
+        <v>-2.798790180472947</v>
       </c>
       <c r="G28">
-        <v>-16.90276606907357</v>
+        <v>-17.57412980698284</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-17.85894270116717</v>
       </c>
       <c r="E29">
-        <v>-41.44662721549916</v>
+        <v>-42.27269106584534</v>
       </c>
       <c r="F29">
-        <v>-3.180689919083395</v>
+        <v>-2.997832785119821</v>
       </c>
       <c r="G29">
-        <v>-17.65146249550745</v>
+        <v>-17.95967594048636</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-17.37612673146148</v>
       </c>
       <c r="E30">
-        <v>-40.92461643121297</v>
+        <v>-42.07805272452167</v>
       </c>
       <c r="F30">
-        <v>-3.23420162493684</v>
+        <v>-2.676076661789631</v>
       </c>
       <c r="G30">
-        <v>-16.78574656062418</v>
+        <v>-18.0053018791086</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-16.90842237519101</v>
       </c>
       <c r="E31">
-        <v>-41.77742544904847</v>
+        <v>-42.17919166300898</v>
       </c>
       <c r="F31">
-        <v>-3.282626326569694</v>
+        <v>-2.741317221699314</v>
       </c>
       <c r="G31">
-        <v>-17.46010634224649</v>
+        <v>-17.88174238794638</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-16.46604900229401</v>
       </c>
       <c r="E32">
-        <v>-41.07263866110169</v>
+        <v>-41.30392367833244</v>
       </c>
       <c r="F32">
-        <v>-3.040650267803124</v>
+        <v>-2.816039274901441</v>
       </c>
       <c r="G32">
-        <v>-17.21575994181119</v>
+        <v>-18.06869386036733</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-16.08328240213188</v>
       </c>
       <c r="E33">
-        <v>-41.12497876368234</v>
+        <v>-41.61682764684044</v>
       </c>
       <c r="F33">
-        <v>-3.729300254242049</v>
+        <v>-2.786516260665667</v>
       </c>
       <c r="G33">
-        <v>-17.34949108414282</v>
+        <v>-18.02924208917583</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-15.77968353852761</v>
       </c>
       <c r="E34">
-        <v>-40.13127986252021</v>
+        <v>-41.17640185027644</v>
       </c>
       <c r="F34">
-        <v>-3.337040124524787</v>
+        <v>-2.892669058232215</v>
       </c>
       <c r="G34">
-        <v>-17.42136964889148</v>
+        <v>-17.58341092140219</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-15.55595702666374</v>
       </c>
       <c r="E35">
-        <v>-41.29390669382747</v>
+        <v>-40.98723843402804</v>
       </c>
       <c r="F35">
-        <v>-3.360661021015615</v>
+        <v>-2.753567118851914</v>
       </c>
       <c r="G35">
-        <v>-17.24605143349552</v>
+        <v>-19.01975731452578</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-15.39274821576573</v>
       </c>
       <c r="E36">
-        <v>-40.54006747542962</v>
+        <v>-40.08018056181766</v>
       </c>
       <c r="F36">
-        <v>-3.717081835050756</v>
+        <v>-2.71565274282578</v>
       </c>
       <c r="G36">
-        <v>-17.91302373274695</v>
+        <v>-18.51353517502474</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-15.29551283459099</v>
       </c>
       <c r="E37">
-        <v>-39.51155593033351</v>
+        <v>-39.95652605056421</v>
       </c>
       <c r="F37">
-        <v>-3.153449057042333</v>
+        <v>-3.101896440096509</v>
       </c>
       <c r="G37">
-        <v>-17.74774971251715</v>
+        <v>-17.85482930798487</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-15.25388405936662</v>
       </c>
       <c r="E38">
-        <v>-39.78528633443816</v>
+        <v>-40.0532836904491</v>
       </c>
       <c r="F38">
-        <v>-3.143475513512627</v>
+        <v>-2.727575434854273</v>
       </c>
       <c r="G38">
-        <v>-18.19768595675949</v>
+        <v>-18.35020775557203</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-15.24543084932485</v>
       </c>
       <c r="E39">
-        <v>-38.42648600911862</v>
+        <v>-38.88949530555887</v>
       </c>
       <c r="F39">
-        <v>-3.048769096717962</v>
+        <v>-2.452044697702505</v>
       </c>
       <c r="G39">
-        <v>-18.43172662893104</v>
+        <v>-18.22127855954511</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-15.23881867385926</v>
       </c>
       <c r="E40">
-        <v>-38.0781467315006</v>
+        <v>-38.53443124403946</v>
       </c>
       <c r="F40">
-        <v>-3.267222834714637</v>
+        <v>-2.723431112738067</v>
       </c>
       <c r="G40">
-        <v>-17.42723759085984</v>
+        <v>-18.25209808324296</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-15.23313139794399</v>
       </c>
       <c r="E41">
-        <v>-36.9453693366149</v>
+        <v>-38.31538895628844</v>
       </c>
       <c r="F41">
-        <v>-3.679407685571434</v>
+        <v>-2.663452342570967</v>
       </c>
       <c r="G41">
-        <v>-18.06239720275164</v>
+        <v>-18.34536111690253</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-15.21531688938843</v>
       </c>
       <c r="E42">
-        <v>-37.69936252312901</v>
+        <v>-38.66974657586265</v>
       </c>
       <c r="F42">
-        <v>-3.213131271679232</v>
+        <v>-2.755285981212722</v>
       </c>
       <c r="G42">
-        <v>-16.93369318550144</v>
+        <v>-19.02004202144215</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-15.16703566225666</v>
       </c>
       <c r="E43">
-        <v>-37.59955722023696</v>
+        <v>-37.45343468519446</v>
       </c>
       <c r="F43">
-        <v>-2.737815712687681</v>
+        <v>-2.729030876380992</v>
       </c>
       <c r="G43">
-        <v>-18.46685648292102</v>
+        <v>-18.41471042485919</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-15.06963603581577</v>
       </c>
       <c r="E44">
-        <v>-36.00855259746311</v>
+        <v>-37.21026242369357</v>
       </c>
       <c r="F44">
-        <v>-3.37006299103739</v>
+        <v>-2.813832504140383</v>
       </c>
       <c r="G44">
-        <v>-18.5804909585565</v>
+        <v>-18.7687914782847</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-14.93594826716546</v>
       </c>
       <c r="E45">
-        <v>-35.39428094798165</v>
+        <v>-37.42997718983473</v>
       </c>
       <c r="F45">
-        <v>-3.317848508536728</v>
+        <v>-2.770628173879972</v>
       </c>
       <c r="G45">
-        <v>-19.39743428128245</v>
+        <v>-18.22864783391553</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-14.7679708723862</v>
       </c>
       <c r="E46">
-        <v>-36.96704487745261</v>
+        <v>-36.74149970102658</v>
       </c>
       <c r="F46">
-        <v>-3.209415215510273</v>
+        <v>-2.590826058897923</v>
       </c>
       <c r="G46">
-        <v>-18.58848592603384</v>
+        <v>-18.73544766361317</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-14.56371465211845</v>
       </c>
       <c r="E47">
-        <v>-36.77588440416682</v>
+        <v>-35.69266889305806</v>
       </c>
       <c r="F47">
-        <v>-3.198648096008685</v>
+        <v>-2.415656174432328</v>
       </c>
       <c r="G47">
-        <v>-19.43848504596941</v>
+        <v>-18.67519407952566</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-14.32438545483091</v>
       </c>
       <c r="E48">
-        <v>-35.77586375328998</v>
+        <v>-35.97048398071763</v>
       </c>
       <c r="F48">
-        <v>-3.125446096990696</v>
+        <v>-2.596205476811703</v>
       </c>
       <c r="G48">
-        <v>-18.49242051557527</v>
+        <v>-18.53702018508033</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-14.07554412143277</v>
       </c>
       <c r="E49">
-        <v>-35.74220134175396</v>
+        <v>-35.50455834701644</v>
       </c>
       <c r="F49">
-        <v>-3.145376616702052</v>
+        <v>-2.540716457967775</v>
       </c>
       <c r="G49">
-        <v>-20.12867585636052</v>
+        <v>-18.434083737355</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.82807438720245</v>
       </c>
       <c r="E50">
-        <v>-35.59337757196588</v>
+        <v>-35.34403073615554</v>
       </c>
       <c r="F50">
-        <v>-3.064053303667016</v>
+        <v>-2.609605147919388</v>
       </c>
       <c r="G50">
-        <v>-18.1027991005129</v>
+        <v>-18.85010675309305</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.58258631041177</v>
       </c>
       <c r="E51">
-        <v>-34.32414593404405</v>
+        <v>-35.19112228281254</v>
       </c>
       <c r="F51">
-        <v>-3.558663196204573</v>
+        <v>-2.453088440630032</v>
       </c>
       <c r="G51">
-        <v>-18.16820885927782</v>
+        <v>-19.01270254198159</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.3454490482059</v>
       </c>
       <c r="E52">
-        <v>-34.88535971781464</v>
+        <v>-34.61569588336888</v>
       </c>
       <c r="F52">
-        <v>-2.851992905285148</v>
+        <v>-2.358030796056581</v>
       </c>
       <c r="G52">
-        <v>-19.10287518138026</v>
+        <v>-18.9613063224844</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.13679823590402</v>
       </c>
       <c r="E53">
-        <v>-34.98461254687776</v>
+        <v>-34.05338847312544</v>
       </c>
       <c r="F53">
-        <v>-3.134316255139873</v>
+        <v>-2.596168200278577</v>
       </c>
       <c r="G53">
-        <v>-19.92350645183696</v>
+        <v>-18.96628538297547</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.9615508390888</v>
       </c>
       <c r="E54">
-        <v>-32.33452465098202</v>
+        <v>-34.04947587158281</v>
       </c>
       <c r="F54">
-        <v>-3.028933839257928</v>
+        <v>-2.529842479071226</v>
       </c>
       <c r="G54">
-        <v>-18.75369208008009</v>
+        <v>-19.0283746645645</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.81026453971243</v>
       </c>
       <c r="E55">
-        <v>-33.14499017260879</v>
+        <v>-33.54711866448991</v>
       </c>
       <c r="F55">
-        <v>-2.73586242235188</v>
+        <v>-2.579007741162182</v>
       </c>
       <c r="G55">
-        <v>-18.11501666882558</v>
+        <v>-19.33131275522659</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.68520454611221</v>
       </c>
       <c r="E56">
-        <v>-34.21417420700478</v>
+        <v>-33.70141735935327</v>
       </c>
       <c r="F56">
-        <v>-3.144327903570108</v>
+        <v>-2.801590062294409</v>
       </c>
       <c r="G56">
-        <v>-19.47805103098201</v>
+        <v>-18.85466206375509</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.59510478346229</v>
       </c>
       <c r="E57">
-        <v>-33.26630119856327</v>
+        <v>-33.20679478586548</v>
       </c>
       <c r="F57">
-        <v>-2.997740007970707</v>
+        <v>-2.589293579202744</v>
       </c>
       <c r="G57">
-        <v>-18.89982783654737</v>
+        <v>-19.2759207072635</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.53688459001091</v>
       </c>
       <c r="E58">
-        <v>-33.67641565435692</v>
+        <v>-32.53568399487674</v>
       </c>
       <c r="F58">
-        <v>-3.013623124551985</v>
+        <v>-2.659226840449286</v>
       </c>
       <c r="G58">
-        <v>-18.65752238743703</v>
+        <v>-19.395289047773</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.49333000451064</v>
       </c>
       <c r="E59">
-        <v>-33.15187118886345</v>
+        <v>-32.85022274250151</v>
       </c>
       <c r="F59">
-        <v>-3.619244189473509</v>
+        <v>-2.883436903528014</v>
       </c>
       <c r="G59">
-        <v>-17.70045360367035</v>
+        <v>-20.17491259063475</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.4673785187532</v>
       </c>
       <c r="E60">
-        <v>-33.6654250479403</v>
+        <v>-32.56032568618948</v>
       </c>
       <c r="F60">
-        <v>-3.013240418811892</v>
+        <v>-2.735089555565068</v>
       </c>
       <c r="G60">
-        <v>-19.18693324316789</v>
+        <v>-19.56331909716425</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.46252092107378</v>
       </c>
       <c r="E61">
-        <v>-34.21139825243808</v>
+        <v>-32.41420767962099</v>
       </c>
       <c r="F61">
-        <v>-3.004327185557769</v>
+        <v>-2.653177273306642</v>
       </c>
       <c r="G61">
-        <v>-18.47270621688891</v>
+        <v>-19.54482307923634</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.47349617073372</v>
       </c>
       <c r="E62">
-        <v>-31.37032875797986</v>
+        <v>-32.25365742639004</v>
       </c>
       <c r="F62">
-        <v>-3.013754006601627</v>
+        <v>-2.707270493076852</v>
       </c>
       <c r="G62">
-        <v>-19.76821041586252</v>
+        <v>-19.72199354486152</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.48299867700568</v>
       </c>
       <c r="E63">
-        <v>-31.6572234360248</v>
+        <v>-32.63406282845638</v>
       </c>
       <c r="F63">
-        <v>-3.232636010545549</v>
+        <v>-2.703853477540304</v>
       </c>
       <c r="G63">
-        <v>-19.58270399656945</v>
+        <v>-19.58023764014269</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.49707631040782</v>
       </c>
       <c r="E64">
-        <v>-31.76516414247163</v>
+        <v>-32.36898180970638</v>
       </c>
       <c r="F64">
-        <v>-3.202325218909712</v>
+        <v>-2.705265015594674</v>
       </c>
       <c r="G64">
-        <v>-19.76659983545766</v>
+        <v>-19.77027785155179</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.51809261805515</v>
       </c>
       <c r="E65">
-        <v>-31.96563062984318</v>
+        <v>-32.0167095524127</v>
       </c>
       <c r="F65">
-        <v>-3.250225563976593</v>
+        <v>-2.897504238762356</v>
       </c>
       <c r="G65">
-        <v>-19.37291969156415</v>
+        <v>-20.02364383330883</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.54130853270983</v>
       </c>
       <c r="E66">
-        <v>-31.78690534618246</v>
+        <v>-31.65338102582929</v>
       </c>
       <c r="F66">
-        <v>-3.374454995007033</v>
+        <v>-2.750144304743546</v>
       </c>
       <c r="G66">
-        <v>-19.42614995329009</v>
+        <v>-20.02879007634963</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.55207574347156</v>
       </c>
       <c r="E67">
-        <v>-32.1176673519397</v>
+        <v>-31.7847452640808</v>
       </c>
       <c r="F67">
-        <v>-3.288106805306615</v>
+        <v>-2.659674987214201</v>
       </c>
       <c r="G67">
-        <v>-19.59504239979432</v>
+        <v>-19.57897466701947</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.55868885814463</v>
       </c>
       <c r="E68">
-        <v>-31.75678872979444</v>
+        <v>-31.46384174623825</v>
       </c>
       <c r="F68">
-        <v>-3.660897815955879</v>
+        <v>-2.718401265868269</v>
       </c>
       <c r="G68">
-        <v>-20.20377558191889</v>
+        <v>-20.00998783295934</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.56315409310482</v>
       </c>
       <c r="E69">
-        <v>-32.5265659124623</v>
+        <v>-32.17214263001497</v>
       </c>
       <c r="F69">
-        <v>-3.444302106043684</v>
+        <v>-3.020576440531084</v>
       </c>
       <c r="G69">
-        <v>-20.2881233164412</v>
+        <v>-19.61137166566677</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.56038885438987</v>
       </c>
       <c r="E70">
-        <v>-30.26505278574273</v>
+        <v>-31.80954998045781</v>
       </c>
       <c r="F70">
-        <v>-3.426838464457865</v>
+        <v>-3.060744804260235</v>
       </c>
       <c r="G70">
-        <v>-18.92092759854191</v>
+        <v>-19.59741109512766</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.53791271308021</v>
       </c>
       <c r="E71">
-        <v>-30.83127959023981</v>
+        <v>-31.95104441506448</v>
       </c>
       <c r="F71">
-        <v>-3.421178229994536</v>
+        <v>-2.834541689210371</v>
       </c>
       <c r="G71">
-        <v>-18.88406467396213</v>
+        <v>-19.94768005536471</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.5053530951503</v>
       </c>
       <c r="E72">
-        <v>-31.82993490620334</v>
+        <v>-31.49165336935636</v>
       </c>
       <c r="F72">
-        <v>-3.461668000275973</v>
+        <v>-2.803691630395312</v>
       </c>
       <c r="G72">
-        <v>-19.23435018692687</v>
+        <v>-20.0429542454394</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.46386770609318</v>
       </c>
       <c r="E73">
-        <v>-32.01312752947263</v>
+        <v>-32.13547557597487</v>
       </c>
       <c r="F73">
-        <v>-3.51897362883424</v>
+        <v>-2.919059186950602</v>
       </c>
       <c r="G73">
-        <v>-18.46213067916371</v>
+        <v>-19.86271986991763</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.40763127178063</v>
       </c>
       <c r="E74">
-        <v>-33.46242940783547</v>
+        <v>-32.03648313416719</v>
       </c>
       <c r="F74">
-        <v>-3.930805595177445</v>
+        <v>-2.829961645840292</v>
       </c>
       <c r="G74">
-        <v>-19.50287350143547</v>
+        <v>-19.64624495237745</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.32580177177159</v>
       </c>
       <c r="E75">
-        <v>-31.69401728733712</v>
+        <v>-32.83936346183112</v>
       </c>
       <c r="F75">
-        <v>-3.737646055825254</v>
+        <v>-3.136503973450666</v>
       </c>
       <c r="G75">
-        <v>-18.80804130619831</v>
+        <v>-20.37494071793583</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.22954118304143</v>
       </c>
       <c r="E76">
-        <v>-31.112416313584</v>
+        <v>-32.27589223376771</v>
       </c>
       <c r="F76">
-        <v>-3.687133868337345</v>
+        <v>-3.258855495578959</v>
       </c>
       <c r="G76">
-        <v>-18.66087597006831</v>
+        <v>-19.26747881613836</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.11979617490564</v>
       </c>
       <c r="E77">
-        <v>-31.36798980115489</v>
+        <v>-33.42711863176066</v>
       </c>
       <c r="F77">
-        <v>-3.460041915064278</v>
+        <v>-3.192188487001655</v>
       </c>
       <c r="G77">
-        <v>-18.402934814376</v>
+        <v>-19.62568149876027</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.99134972118064</v>
       </c>
       <c r="E78">
-        <v>-32.5451620909748</v>
+        <v>-33.27699292569537</v>
       </c>
       <c r="F78">
-        <v>-3.88102816957582</v>
+        <v>-3.300081684481484</v>
       </c>
       <c r="G78">
-        <v>-18.63136245658571</v>
+        <v>-19.82448472421181</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.83663161671923</v>
       </c>
       <c r="E79">
-        <v>-32.92350250889363</v>
+        <v>-32.74739015473533</v>
       </c>
       <c r="F79">
-        <v>-3.57670918007456</v>
+        <v>-3.288100178367392</v>
       </c>
       <c r="G79">
-        <v>-17.85514712035664</v>
+        <v>-19.48126060488234</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.66984766375163</v>
       </c>
       <c r="E80">
-        <v>-32.34258080624166</v>
+        <v>-33.4211184037005</v>
       </c>
       <c r="F80">
-        <v>-3.974834151003642</v>
+        <v>-3.486903384834857</v>
       </c>
       <c r="G80">
-        <v>-18.61672487948382</v>
+        <v>-19.58771947306145</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.49321651286173</v>
       </c>
       <c r="E81">
-        <v>-33.30381281300581</v>
+        <v>-34.00661612933722</v>
       </c>
       <c r="F81">
-        <v>-3.504318981111314</v>
+        <v>-3.422698284178673</v>
       </c>
       <c r="G81">
-        <v>-17.81400697094012</v>
+        <v>-19.16348795965877</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.30302351384328</v>
       </c>
       <c r="E82">
-        <v>-34.12724335571654</v>
+        <v>-33.78300687554947</v>
       </c>
       <c r="F82">
-        <v>-3.978232114089925</v>
+        <v>-3.444806581791989</v>
       </c>
       <c r="G82">
-        <v>-17.99163925766802</v>
+        <v>-19.00307216500785</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.09766213449257</v>
       </c>
       <c r="E83">
-        <v>-34.81234260291496</v>
+        <v>-34.98756284769375</v>
       </c>
       <c r="F83">
-        <v>-4.421712685424488</v>
+        <v>-3.352336756984883</v>
       </c>
       <c r="G83">
-        <v>-17.58401013014479</v>
+        <v>-19.3793818764568</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.89276321435789</v>
       </c>
       <c r="E84">
-        <v>-33.51757263582687</v>
+        <v>-35.74708982944524</v>
       </c>
       <c r="F84">
-        <v>-4.147076585067743</v>
+        <v>-3.484530940593239</v>
       </c>
       <c r="G84">
-        <v>-17.03791578016878</v>
+        <v>-18.42404119746162</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.69289484305638</v>
       </c>
       <c r="E85">
-        <v>-36.12585139544679</v>
+        <v>-35.93624645298264</v>
       </c>
       <c r="F85">
-        <v>-4.020079578544551</v>
+        <v>-3.570213122901806</v>
       </c>
       <c r="G85">
-        <v>-16.85432451147018</v>
+        <v>-18.84874777414918</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.49533469802884</v>
       </c>
       <c r="E86">
-        <v>-37.31981753112414</v>
+        <v>-36.52298950897146</v>
       </c>
       <c r="F86">
-        <v>-3.750518056897355</v>
+        <v>-3.550938670173467</v>
       </c>
       <c r="G86">
-        <v>-17.15704079558114</v>
+        <v>-19.14976574839849</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.30516855324854</v>
       </c>
       <c r="E87">
-        <v>-38.26127369189678</v>
+        <v>-37.18327951131887</v>
       </c>
       <c r="F87">
-        <v>-4.43504940060956</v>
+        <v>-3.541015657055332</v>
       </c>
       <c r="G87">
-        <v>-17.39886456031551</v>
+        <v>-18.45433599969149</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.13875038924215</v>
       </c>
       <c r="E88">
-        <v>-37.28890163907377</v>
+        <v>-37.88575904175873</v>
       </c>
       <c r="F88">
-        <v>-4.254990491732642</v>
+        <v>-3.762128454414993</v>
       </c>
       <c r="G88">
-        <v>-17.01118146966639</v>
+        <v>-18.77603495192463</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.00284769977966</v>
       </c>
       <c r="E89">
-        <v>-39.13683602738381</v>
+        <v>-39.16007389175417</v>
       </c>
       <c r="F89">
-        <v>-4.007292070947535</v>
+        <v>-3.572698225110205</v>
       </c>
       <c r="G89">
-        <v>-17.32157159833738</v>
+        <v>-18.10726502644538</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.893970700548499</v>
       </c>
       <c r="E90">
-        <v>-39.191850193866</v>
+        <v>-40.39896928229862</v>
       </c>
       <c r="F90">
-        <v>-4.772404510501867</v>
+        <v>-3.830873008438518</v>
       </c>
       <c r="G90">
-        <v>-16.78768488503743</v>
+        <v>-18.77485639771265</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.821875377171814</v>
       </c>
       <c r="E91">
-        <v>-41.16593654684472</v>
+        <v>-40.5164401622946</v>
       </c>
       <c r="F91">
-        <v>-4.605454515774252</v>
+        <v>-3.859611558743842</v>
       </c>
       <c r="G91">
-        <v>-17.0933111386774</v>
+        <v>-17.88620500333332</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.800765499512117</v>
       </c>
       <c r="E92">
-        <v>-41.88265812803871</v>
+        <v>-41.78046858358162</v>
       </c>
       <c r="F92">
-        <v>-3.734892562578348</v>
+        <v>-3.747080332175737</v>
       </c>
       <c r="G92">
-        <v>-17.78787683499865</v>
+        <v>-18.39429263524573</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.836014999051264</v>
       </c>
       <c r="E93">
-        <v>-42.79118322582757</v>
+        <v>-42.72318366012839</v>
       </c>
       <c r="F93">
-        <v>-4.783833495558292</v>
+        <v>-4.131152050116325</v>
       </c>
       <c r="G93">
-        <v>-17.25248382347833</v>
+        <v>-18.0582672971914</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.918833149676258</v>
       </c>
       <c r="E94">
-        <v>-44.47933493725098</v>
+        <v>-43.56280349741655</v>
       </c>
       <c r="F94">
-        <v>-4.504137727105247</v>
+        <v>-3.902976592280396</v>
       </c>
       <c r="G94">
-        <v>-18.33300781622274</v>
+        <v>-18.43983581022949</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.05804337581717</v>
       </c>
       <c r="E95">
-        <v>-45.38327269087006</v>
+        <v>-45.24540329970655</v>
       </c>
       <c r="F95">
-        <v>-4.600807374644547</v>
+        <v>-4.254050294730465</v>
       </c>
       <c r="G95">
-        <v>-17.59175349616115</v>
+        <v>-18.29536360289569</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.26325991557965</v>
       </c>
       <c r="E96">
-        <v>-46.8591385977619</v>
+        <v>-47.01024018997584</v>
       </c>
       <c r="F96">
-        <v>-4.904270660618715</v>
+        <v>-4.232000811202748</v>
       </c>
       <c r="G96">
-        <v>-17.84026290761208</v>
+        <v>-18.87938852838791</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.5254848838438</v>
       </c>
       <c r="E97">
-        <v>-47.87175519909108</v>
+        <v>-47.37601409252338</v>
       </c>
       <c r="F97">
-        <v>-4.62354191801438</v>
+        <v>-4.569190247614495</v>
       </c>
       <c r="G97">
-        <v>-17.51346240470292</v>
+        <v>-18.73438497849506</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.83965396153104</v>
       </c>
       <c r="E98">
-        <v>-49.73081038744545</v>
+        <v>-49.76693742096015</v>
       </c>
       <c r="F98">
-        <v>-4.816568918582123</v>
+        <v>-4.38161307618977</v>
       </c>
       <c r="G98">
-        <v>-18.85542017868358</v>
+        <v>-18.77251584201639</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.19318831918051</v>
       </c>
       <c r="E99">
-        <v>-51.72481976182092</v>
+        <v>-50.72865850291711</v>
       </c>
       <c r="F99">
-        <v>-5.576674705553935</v>
+        <v>-4.799869031741685</v>
       </c>
       <c r="G99">
-        <v>-17.50568593323118</v>
+        <v>-19.03839237536633</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.60954500053532</v>
       </c>
       <c r="E100">
-        <v>-51.92812447027678</v>
+        <v>-52.52896466585148</v>
       </c>
       <c r="F100">
-        <v>-5.119299099404813</v>
+        <v>-4.773881489581059</v>
       </c>
       <c r="G100">
-        <v>-18.0077003693518</v>
+        <v>-19.11647159191005</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.03779116528271</v>
       </c>
       <c r="E101">
-        <v>-53.28133213019685</v>
+        <v>-54.05703595322224</v>
       </c>
       <c r="F101">
-        <v>-6.126420732421827</v>
+        <v>-4.87206373599787</v>
       </c>
       <c r="G101">
-        <v>-18.80131096711697</v>
+        <v>-18.97181399402605</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.52782336529273</v>
       </c>
       <c r="E102">
-        <v>-56.33421193941584</v>
+        <v>-55.51608310764959</v>
       </c>
       <c r="F102">
-        <v>-5.988848787634496</v>
+        <v>-5.208358535614594</v>
       </c>
       <c r="G102">
-        <v>-18.39349644904354</v>
+        <v>-19.39039771673873</v>
       </c>
     </row>
   </sheetData>
